--- a/data/trans_orig/P45C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P45C-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2007</t>
+          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2007 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>558568</t>
+          <t>557274</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>597186</t>
+          <t>597506</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>607574</t>
+          <t>608771</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>636984</t>
+          <t>637246</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1177484</t>
+          <t>1175672</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1228115</t>
+          <t>1225824</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92915</t>
+          <t>92196</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131776</t>
+          <t>132311</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50483</t>
+          <t>50694</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79216</t>
+          <t>79015</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>151352</t>
+          <t>151823</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200240</t>
+          <t>200636</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10480</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>952</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11023</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>774247</t>
+          <t>773372</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>822750</t>
+          <t>822417</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>830168</t>
+          <t>831768</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>871239</t>
+          <t>871292</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1618199</t>
+          <t>1620196</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1680056</t>
+          <t>1680610</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,38%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>123126</t>
+          <t>123731</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>169631</t>
+          <t>170999</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>79821</t>
+          <t>80021</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>120269</t>
+          <t>118565</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>215224</t>
+          <t>214966</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>274626</t>
+          <t>272710</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7807</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24279</t>
+          <t>23458</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>8385</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25033</t>
+          <t>24144</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19156</t>
+          <t>19823</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41013</t>
+          <t>41901</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>558576</t>
+          <t>557988</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>595832</t>
+          <t>596181</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>563462</t>
+          <t>564898</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>599088</t>
+          <t>600077</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1137040</t>
+          <t>1133353</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1187051</t>
+          <t>1185900</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,21%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64604</t>
+          <t>64858</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98105</t>
+          <t>97666</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66648</t>
+          <t>65868</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99709</t>
+          <t>99693</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>139034</t>
+          <t>139925</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>184210</t>
+          <t>188723</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11060</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29948</t>
+          <t>30153</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10247</t>
+          <t>10703</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27892</t>
+          <t>28149</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25094</t>
+          <t>25603</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49854</t>
+          <t>50210</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>776945</t>
+          <t>777067</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>817821</t>
+          <t>818067</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>869367</t>
+          <t>870581</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>913218</t>
+          <t>914274</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1659886</t>
+          <t>1659441</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1720993</t>
+          <t>1721283</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,14%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103668</t>
+          <t>103063</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>141172</t>
+          <t>142044</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99930</t>
+          <t>99051</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142983</t>
+          <t>139563</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>214765</t>
+          <t>212985</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>269685</t>
+          <t>269809</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12148</t>
+          <t>12190</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29695</t>
+          <t>30908</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>14864</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34343</t>
+          <t>34015</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30885</t>
+          <t>30694</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57954</t>
+          <t>57536</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2715376</t>
+          <t>2710294</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2798029</t>
+          <t>2797571</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2914915</t>
+          <t>2913396</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2990517</t>
+          <t>2986825</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5649348</t>
+          <t>5648749</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5766251</t>
+          <t>5766669</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>418229</t>
+          <t>418862</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>500237</t>
+          <t>500495</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>327798</t>
+          <t>327905</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>400883</t>
+          <t>398378</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>770046</t>
+          <t>765457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>875580</t>
+          <t>876218</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41158</t>
+          <t>41915</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71594</t>
+          <t>72746</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42023</t>
+          <t>43297</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71951</t>
+          <t>73097</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>92764</t>
+          <t>91197</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>135990</t>
+          <t>133070</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2012</t>
+          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2012 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>553735</t>
+          <t>551439</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>593450</t>
+          <t>591472</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>578669</t>
+          <t>582078</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>618848</t>
+          <t>618473</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1144814</t>
+          <t>1145935</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1201045</t>
+          <t>1199795</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,14%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91618</t>
+          <t>94699</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131612</t>
+          <t>132822</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62857</t>
+          <t>63565</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99681</t>
+          <t>98187</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>165450</t>
+          <t>167184</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>217422</t>
+          <t>216564</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>6996</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22548</t>
+          <t>21640</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>7610</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23323</t>
+          <t>23914</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19134</t>
+          <t>18678</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42076</t>
+          <t>40242</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>819868</t>
+          <t>824310</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>869428</t>
+          <t>868903</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>866823</t>
+          <t>869441</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>910805</t>
+          <t>909997</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1705767</t>
+          <t>1702598</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1768140</t>
+          <t>1769005</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,18%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>124349</t>
+          <t>126210</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>171220</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>96257</t>
+          <t>97076</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>138304</t>
+          <t>138055</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>234558</t>
+          <t>232071</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>295085</t>
+          <t>295252</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23441</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>8350</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24562</t>
+          <t>22817</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19027</t>
+          <t>18267</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42894</t>
+          <t>41473</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>590439</t>
+          <t>591864</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>633993</t>
+          <t>636103</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>637242</t>
+          <t>637368</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>677635</t>
+          <t>676809</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1242394</t>
+          <t>1242745</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1300325</t>
+          <t>1301204</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,78%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>105988</t>
+          <t>104548</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>147424</t>
+          <t>146207</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84767</t>
+          <t>85859</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123696</t>
+          <t>125181</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>198998</t>
+          <t>200150</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>256448</t>
+          <t>257895</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18099</t>
+          <t>17944</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12334</t>
+          <t>13152</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9735</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26337</t>
+          <t>26172</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>740493</t>
+          <t>739645</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>790821</t>
+          <t>789357</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>875418</t>
+          <t>875166</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>919530</t>
+          <t>918596</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1633941</t>
+          <t>1634841</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1697177</t>
+          <t>1698542</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,63%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>148410</t>
+          <t>147858</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>197697</t>
+          <t>197014</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100298</t>
+          <t>100936</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>140733</t>
+          <t>141109</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>260020</t>
+          <t>258928</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>320698</t>
+          <t>320004</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>2783</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>13333</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13056</t>
+          <t>13826</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31762</t>
+          <t>33667</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19013</t>
+          <t>19352</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39988</t>
+          <t>40545</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2756401</t>
+          <t>2757294</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2845146</t>
+          <t>2847854</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3007026</t>
+          <t>3008035</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3092545</t>
+          <t>3091474</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5787084</t>
+          <t>5786272</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5907200</t>
+          <t>5910210</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>508777</t>
+          <t>508366</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>596814</t>
+          <t>598366</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>379623</t>
+          <t>378936</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>455893</t>
+          <t>459093</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>917121</t>
+          <t>913835</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1031628</t>
+          <t>1027388</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32497</t>
+          <t>32323</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59551</t>
+          <t>60314</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42517</t>
+          <t>41378</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72634</t>
+          <t>72597</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82646</t>
+          <t>82768</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>121592</t>
+          <t>124239</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2016</t>
+          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2016 (tasa de respuesta: 99,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>600621</t>
+          <t>603421</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>631616</t>
+          <t>632053</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>603045</t>
+          <t>603125</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>630619</t>
+          <t>630393</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1217971</t>
+          <t>1216198</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1256183</t>
+          <t>1255227</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35316</t>
+          <t>35065</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65283</t>
+          <t>62644</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33634</t>
+          <t>33507</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58497</t>
+          <t>59676</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74464</t>
+          <t>73364</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109727</t>
+          <t>111862</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12588</t>
+          <t>13221</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13968</t>
+          <t>13777</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>7881</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22507</t>
+          <t>22182</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>856858</t>
+          <t>855589</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>901484</t>
+          <t>902578</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>888569</t>
+          <t>887598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>930933</t>
+          <t>929614</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1760737</t>
+          <t>1761233</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1823734</t>
+          <t>1824716</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,05%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>104543</t>
+          <t>102770</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>146265</t>
+          <t>149358</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93467</t>
+          <t>93790</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>134753</t>
+          <t>134342</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>205276</t>
+          <t>205909</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>265908</t>
+          <t>267094</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>15560</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22510</t>
+          <t>23860</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11700</t>
+          <t>12593</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31286</t>
+          <t>32328</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>611405</t>
+          <t>610312</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>651927</t>
+          <t>651325</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>612154</t>
+          <t>610847</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>655352</t>
+          <t>657570</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1237050</t>
+          <t>1236670</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1297573</t>
+          <t>1295372</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,96%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>86041</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125351</t>
+          <t>125426</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109681</t>
+          <t>109455</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>152258</t>
+          <t>152598</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>205969</t>
+          <t>209300</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>262742</t>
+          <t>265629</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21940</t>
+          <t>21897</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>17953</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13427</t>
+          <t>14592</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33544</t>
+          <t>34835</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>755959</t>
+          <t>754460</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>799660</t>
+          <t>800650</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>852033</t>
+          <t>854180</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>898986</t>
+          <t>899013</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1625189</t>
+          <t>1621754</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1687481</t>
+          <t>1688082</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,82%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125924</t>
+          <t>124627</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169047</t>
+          <t>170664</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129547</t>
+          <t>127342</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174550</t>
+          <t>172934</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>264941</t>
+          <t>265025</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>327503</t>
+          <t>329231</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>11003</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16704</t>
+          <t>16236</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23095</t>
+          <t>23493</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2864354</t>
+          <t>2868558</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2948237</t>
+          <t>2953974</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,49 +7596,49 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>87,78%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>3040762</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>3001178</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3082182</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>86,43%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>85,3%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
           <t>87,61%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2852</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3040762</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>3001273</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>3081033</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>86,43%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>85,31%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>87,57%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>5633</t>
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5890471</t>
+          <t>5896891</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6012886</t>
+          <t>6007079</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>387485</t>
+          <t>381603</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>468427</t>
+          <t>461787</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>399464</t>
+          <t>398811</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>477621</t>
+          <t>478903</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>801589</t>
+          <t>807294</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>918331</t>
+          <t>912590</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20462</t>
+          <t>21110</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44332</t>
+          <t>45565</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28480</t>
+          <t>28262</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54585</t>
+          <t>53496</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54591</t>
+          <t>55294</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>89984</t>
+          <t>91240</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2023</t>
+          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>463488</t>
+          <t>461308</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>518236</t>
+          <t>518522</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>542536</t>
+          <t>543945</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>575666</t>
+          <t>575275</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1017024</t>
+          <t>1021343</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1082779</t>
+          <t>1086363</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,15%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105939</t>
+          <t>105441</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>161251</t>
+          <t>162524</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87124</t>
+          <t>87883</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>117810</t>
+          <t>118415</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>204625</t>
+          <t>201783</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>269357</t>
+          <t>265805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14144</t>
+          <t>13839</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21836</t>
+          <t>20872</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12201</t>
+          <t>11571</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30291</t>
+          <t>29527</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1007836</t>
+          <t>1005248</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1121933</t>
+          <t>1123599</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>793576</t>
+          <t>792943</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>833635</t>
+          <t>833857</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1821827</t>
+          <t>1820396</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1954530</t>
+          <t>1961373</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,26%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58419</t>
+          <t>62490</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>160630</t>
+          <t>164489</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>109038</t>
+          <t>108304</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>146842</t>
+          <t>147427</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>166381</t>
+          <t>166082</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>288857</t>
+          <t>290542</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7835</t>
+          <t>7224</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30970</t>
+          <t>31553</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9267</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23461</t>
+          <t>24441</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22249</t>
+          <t>20389</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49648</t>
+          <t>49604</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>546618</t>
+          <t>546142</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>597142</t>
+          <t>599326</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>808365</t>
+          <t>804716</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>888683</t>
+          <t>887397</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1366515</t>
+          <t>1368590</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1500480</t>
+          <t>1496031</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92320</t>
+          <t>90555</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>138100</t>
+          <t>139127</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34025</t>
+          <t>37058</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102178</t>
+          <t>106298</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122444</t>
+          <t>120660</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>232962</t>
+          <t>229225</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27777</t>
+          <t>27518</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>6973</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28001</t>
+          <t>28502</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19253</t>
+          <t>19183</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48469</t>
+          <t>47526</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>770116</t>
+          <t>771703</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>817915</t>
+          <t>819197</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>970481</t>
+          <t>970467</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1015684</t>
+          <t>1014120</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1755525</t>
+          <t>1759341</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1823716</t>
+          <t>1824392</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94218</t>
+          <t>92574</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>137901</t>
+          <t>137196</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73163</t>
+          <t>73731</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117886</t>
+          <t>117511</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>179320</t>
+          <t>176879</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>243377</t>
+          <t>239394</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9054</t>
+          <t>8777</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25159</t>
+          <t>25431</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12005</t>
+          <t>12363</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14572</t>
+          <t>14712</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>32680</t>
+          <t>33561</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2856241</t>
+          <t>2850514</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3024612</t>
+          <t>3036571</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3158006</t>
+          <t>3160073</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3287351</t>
+          <t>3291561</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6044835</t>
+          <t>6040436</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6255466</t>
+          <t>6261619</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>376730</t>
+          <t>368642</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>537618</t>
+          <t>540816</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>326841</t>
+          <t>319593</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>445398</t>
+          <t>442190</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>756719</t>
+          <t>760892</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>952492</t>
+          <t>956689</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38688</t>
+          <t>39776</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74710</t>
+          <t>77503</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39338</t>
+          <t>38216</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67432</t>
+          <t>67394</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>85001</t>
+          <t>84783</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>134634</t>
+          <t>132144</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P45C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P45C-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>557274</t>
+          <t>558565</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>597506</t>
+          <t>599067</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>608771</t>
+          <t>607714</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>637246</t>
+          <t>636691</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1175672</t>
+          <t>1179772</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1225824</t>
+          <t>1224792</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,67%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92196</t>
+          <t>92655</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132311</t>
+          <t>131529</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50694</t>
+          <t>50821</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79015</t>
+          <t>79264</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>151823</t>
+          <t>152225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200636</t>
+          <t>196969</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>773372</t>
+          <t>774787</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>822417</t>
+          <t>821723</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>831768</t>
+          <t>829779</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>871292</t>
+          <t>870494</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1620196</t>
+          <t>1621703</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1680610</t>
+          <t>1681992</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,45%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>123731</t>
+          <t>123374</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>170999</t>
+          <t>168174</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80021</t>
+          <t>80199</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>118565</t>
+          <t>117009</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>214966</t>
+          <t>216348</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>272710</t>
+          <t>271225</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>7770</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23458</t>
+          <t>24822</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8385</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24144</t>
+          <t>24048</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19823</t>
+          <t>18575</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41901</t>
+          <t>41723</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>557988</t>
+          <t>559158</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>596181</t>
+          <t>597414</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>564898</t>
+          <t>564450</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>600077</t>
+          <t>600689</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1133353</t>
+          <t>1136079</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1185900</t>
+          <t>1187299</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,31%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64858</t>
+          <t>63316</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97666</t>
+          <t>98620</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65868</t>
+          <t>66799</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99693</t>
+          <t>100391</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>139925</t>
+          <t>139865</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>188723</t>
+          <t>186936</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11000</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30153</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10703</t>
+          <t>10098</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28149</t>
+          <t>26246</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25603</t>
+          <t>25460</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50210</t>
+          <t>50536</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>777067</t>
+          <t>777057</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>818067</t>
+          <t>817831</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>870581</t>
+          <t>868161</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>914274</t>
+          <t>914608</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1659441</t>
+          <t>1659608</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1721283</t>
+          <t>1720730</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,11%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103063</t>
+          <t>104555</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>142044</t>
+          <t>143138</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99051</t>
+          <t>101692</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139563</t>
+          <t>143776</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>212985</t>
+          <t>214872</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>269809</t>
+          <t>270448</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12190</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30908</t>
+          <t>30999</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14864</t>
+          <t>14883</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34015</t>
+          <t>33533</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30694</t>
+          <t>31681</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57536</t>
+          <t>58321</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2710294</t>
+          <t>2711579</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2797571</t>
+          <t>2796625</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2913396</t>
+          <t>2911106</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2986825</t>
+          <t>2990281</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5648749</t>
+          <t>5650892</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5766669</t>
+          <t>5759745</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,74%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>418862</t>
+          <t>417405</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>500495</t>
+          <t>501386</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>327905</t>
+          <t>328046</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>398378</t>
+          <t>398532</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>765457</t>
+          <t>771904</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>876218</t>
+          <t>871480</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41915</t>
+          <t>41443</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72746</t>
+          <t>72470</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43297</t>
+          <t>42484</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73097</t>
+          <t>72232</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>91197</t>
+          <t>92113</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>133070</t>
+          <t>136039</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>551439</t>
+          <t>551334</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>591472</t>
+          <t>592884</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>582078</t>
+          <t>581243</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>618473</t>
+          <t>619139</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1145935</t>
+          <t>1143825</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1199795</t>
+          <t>1198925</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,08%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94699</t>
+          <t>93395</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132822</t>
+          <t>132545</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63565</t>
+          <t>63493</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98187</t>
+          <t>98304</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>167184</t>
+          <t>167660</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>216564</t>
+          <t>223386</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21640</t>
+          <t>22229</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7610</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23914</t>
+          <t>24092</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18678</t>
+          <t>19127</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40242</t>
+          <t>40540</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>824310</t>
+          <t>822415</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>868903</t>
+          <t>870189</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>869441</t>
+          <t>866606</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>909997</t>
+          <t>910632</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1702598</t>
+          <t>1704217</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1769005</t>
+          <t>1768622</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>126210</t>
+          <t>126371</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>171220</t>
+          <t>170570</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>97076</t>
+          <t>97549</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>138055</t>
+          <t>139595</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>232071</t>
+          <t>232336</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>295252</t>
+          <t>292824</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>23267</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8350</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22817</t>
+          <t>25346</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18267</t>
+          <t>19942</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41473</t>
+          <t>41843</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>591864</t>
+          <t>588756</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>636103</t>
+          <t>633381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>637368</t>
+          <t>640429</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>676809</t>
+          <t>679039</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1242745</t>
+          <t>1239567</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1301204</t>
+          <t>1298241</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,58%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>104548</t>
+          <t>106530</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>146207</t>
+          <t>149941</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85859</t>
+          <t>84387</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125181</t>
+          <t>122139</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200150</t>
+          <t>202160</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>257895</t>
+          <t>258759</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17944</t>
+          <t>18085</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,82 +4398,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>6014</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2212</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>12091</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>16344</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>9944</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>25679</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>6014</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2771</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>13152</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>16344</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>9808</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>26172</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>739645</t>
+          <t>740766</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>789357</t>
+          <t>787267</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>875166</t>
+          <t>876137</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>918596</t>
+          <t>921109</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1634841</t>
+          <t>1633356</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1698542</t>
+          <t>1697974</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,6%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147858</t>
+          <t>149811</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>197014</t>
+          <t>195435</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100936</t>
+          <t>98987</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>141109</t>
+          <t>141874</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>258928</t>
+          <t>259573</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>320004</t>
+          <t>320245</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13333</t>
+          <t>13379</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13826</t>
+          <t>12931</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33667</t>
+          <t>32138</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19352</t>
+          <t>18986</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>40545</t>
+          <t>39295</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2757294</t>
+          <t>2755487</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2847854</t>
+          <t>2847553</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3008035</t>
+          <t>3006014</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3091474</t>
+          <t>3085325</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5786272</t>
+          <t>5790644</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5910210</t>
+          <t>5910279</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>508366</t>
+          <t>507133</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>598366</t>
+          <t>598562</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>378936</t>
+          <t>382536</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>459093</t>
+          <t>458186</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>913835</t>
+          <t>910374</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1027388</t>
+          <t>1031273</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32323</t>
+          <t>31878</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60314</t>
+          <t>59707</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41378</t>
+          <t>41573</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72597</t>
+          <t>72617</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82768</t>
+          <t>79250</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>124239</t>
+          <t>120888</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>603421</t>
+          <t>600818</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>632053</t>
+          <t>631759</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>603125</t>
+          <t>604300</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>630393</t>
+          <t>630817</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1216198</t>
+          <t>1216561</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1255227</t>
+          <t>1255035</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35065</t>
+          <t>36092</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62644</t>
+          <t>64702</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33507</t>
+          <t>32658</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59676</t>
+          <t>56406</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73364</t>
+          <t>74598</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111862</t>
+          <t>111727</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13221</t>
+          <t>13387</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13777</t>
+          <t>13577</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>8237</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22182</t>
+          <t>22090</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>855589</t>
+          <t>856140</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>902578</t>
+          <t>903446</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>887598</t>
+          <t>887398</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>929614</t>
+          <t>930600</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1761233</t>
+          <t>1758252</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1824716</t>
+          <t>1819225</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,79%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>102770</t>
+          <t>103319</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>149358</t>
+          <t>147796</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93790</t>
+          <t>94375</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>134342</t>
+          <t>134590</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>205909</t>
+          <t>209218</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>267094</t>
+          <t>267774</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15560</t>
+          <t>15638</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23860</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12593</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32328</t>
+          <t>31810</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>610312</t>
+          <t>611076</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>651325</t>
+          <t>651692</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>610847</t>
+          <t>610546</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>657570</t>
+          <t>655614</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1236670</t>
+          <t>1234664</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1295372</t>
+          <t>1296544</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,04%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86041</t>
+          <t>87426</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125426</t>
+          <t>125323</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109455</t>
+          <t>110428</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>152598</t>
+          <t>153645</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>209300</t>
+          <t>205866</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>265629</t>
+          <t>265862</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>22075</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5044</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17953</t>
+          <t>18098</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14592</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34835</t>
+          <t>34294</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>754460</t>
+          <t>758305</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>800650</t>
+          <t>802449</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>854180</t>
+          <t>851042</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>899013</t>
+          <t>899134</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1621754</t>
+          <t>1623876</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1688082</t>
+          <t>1687332</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,78%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124627</t>
+          <t>123321</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170664</t>
+          <t>166859</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127342</t>
+          <t>128952</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>172934</t>
+          <t>175418</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>265025</t>
+          <t>267097</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>329231</t>
+          <t>328972</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11003</t>
+          <t>10854</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16236</t>
+          <t>15558</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8903</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23493</t>
+          <t>23808</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2868558</t>
+          <t>2872186</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2953974</t>
+          <t>2953273</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3001178</t>
+          <t>2997251</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3082182</t>
+          <t>3080889</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5896891</t>
+          <t>5892567</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6007079</t>
+          <t>6007281</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>381603</t>
+          <t>382515</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>461787</t>
+          <t>461252</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>398811</t>
+          <t>400362</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>478903</t>
+          <t>478364</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>807294</t>
+          <t>807743</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>912590</t>
+          <t>914266</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21110</t>
+          <t>19928</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45565</t>
+          <t>43526</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28262</t>
+          <t>27888</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53496</t>
+          <t>52384</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55294</t>
+          <t>53130</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91240</t>
+          <t>88717</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>494807</t>
+          <t>538986</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>461308</t>
+          <t>511850</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>518522</t>
+          <t>561708</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>560339</t>
+          <t>610180</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>543945</t>
+          <t>593154</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>575275</t>
+          <t>627575</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1055146</t>
+          <t>1149166</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1021343</t>
+          <t>1115777</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1086363</t>
+          <t>1178559</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,06%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>130326</t>
+          <t>141160</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105441</t>
+          <t>118748</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>162524</t>
+          <t>168628</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>101758</t>
+          <t>109231</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87883</t>
+          <t>93869</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>118415</t>
+          <t>126554</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>232084</t>
+          <t>250390</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>201783</t>
+          <t>219939</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>265805</t>
+          <t>283574</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13839</t>
+          <t>13901</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12724</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20872</t>
+          <t>20427</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>19291</t>
+          <t>19338</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11571</t>
+          <t>11814</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29527</t>
+          <t>29717</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>631699</t>
+          <t>686809</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>631699</t>
+          <t>686809</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>631699</t>
+          <t>686809</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>674821</t>
+          <t>732085</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>674821</t>
+          <t>732085</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>674821</t>
+          <t>732085</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1306521</t>
+          <t>1418894</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1306521</t>
+          <t>1418894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1306521</t>
+          <t>1418894</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1054487</t>
+          <t>889154</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1005248</t>
+          <t>860189</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1123599</t>
+          <t>916119</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>815094</t>
+          <t>914116</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>792943</t>
+          <t>892516</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>833857</t>
+          <t>932621</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1869581</t>
+          <t>1803270</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1820396</t>
+          <t>1767165</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1961373</t>
+          <t>1838979</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>86,83%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>119185</t>
+          <t>139026</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62490</t>
+          <t>115675</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>164489</t>
+          <t>167571</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126375</t>
+          <t>138457</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>108304</t>
+          <t>120784</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>147427</t>
+          <t>159965</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>245560</t>
+          <t>277483</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>166082</t>
+          <t>244135</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>290542</t>
+          <t>311478</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18065</t>
+          <t>19549</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7224</t>
+          <t>10976</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31553</t>
+          <t>32260</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15977</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>11089</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24441</t>
+          <t>27461</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>34042</t>
+          <t>37054</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20389</t>
+          <t>25669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49604</t>
+          <t>52669</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1191737</t>
+          <t>1047729</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1191737</t>
+          <t>1047729</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1191737</t>
+          <t>1047729</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>957446</t>
+          <t>1070078</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>957446</t>
+          <t>1070078</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>957446</t>
+          <t>1070078</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2149183</t>
+          <t>2117807</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2149183</t>
+          <t>2117807</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2149183</t>
+          <t>2117807</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,32 +9176,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>573599</t>
+          <t>652259</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>546142</t>
+          <t>623980</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>599326</t>
+          <t>677943</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>840595</t>
+          <t>701936</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>804716</t>
+          <t>680372</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>887397</t>
+          <t>718429</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1414194</t>
+          <t>1354195</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1368590</t>
+          <t>1320977</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1496031</t>
+          <t>1386075</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>86,04%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>113577</t>
+          <t>130347</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90555</t>
+          <t>106835</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>139127</t>
+          <t>157847</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>75549</t>
+          <t>88272</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37058</t>
+          <t>72737</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>106298</t>
+          <t>109437</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>189125</t>
+          <t>218619</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120660</t>
+          <t>189619</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>229225</t>
+          <t>250020</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -9402,22 +9402,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15087</t>
+          <t>18060</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27518</t>
+          <t>30258</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16468</t>
+          <t>20005</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>12935</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28502</t>
+          <t>31256</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>31554</t>
+          <t>38065</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19183</t>
+          <t>25859</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47526</t>
+          <t>54464</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>702262</t>
+          <t>800667</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>702262</t>
+          <t>800667</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>702262</t>
+          <t>800667</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>932611</t>
+          <t>810212</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>932611</t>
+          <t>810212</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>932611</t>
+          <t>810212</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1634873</t>
+          <t>1610879</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1634873</t>
+          <t>1610879</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1634873</t>
+          <t>1610879</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>797620</t>
+          <t>846669</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>771703</t>
+          <t>819850</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>819197</t>
+          <t>868903</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>992649</t>
+          <t>1007038</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>970467</t>
+          <t>985110</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1014120</t>
+          <t>1026429</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1790270</t>
+          <t>1853707</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1759341</t>
+          <t>1820432</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1824392</t>
+          <t>1885648</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,44%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>113641</t>
+          <t>127460</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92574</t>
+          <t>105862</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>137196</t>
+          <t>151766</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>95065</t>
+          <t>104003</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73731</t>
+          <t>85941</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117511</t>
+          <t>125110</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>208706</t>
+          <t>231462</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>176879</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>239394</t>
+          <t>263660</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15570</t>
+          <t>15933</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8777</t>
+          <t>9466</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25431</t>
+          <t>25902</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6527</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12363</t>
+          <t>13095</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>22097</t>
+          <t>23176</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14712</t>
+          <t>15578</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>33561</t>
+          <t>33747</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1094242</t>
+          <t>1118283</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1094242</t>
+          <t>1118283</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1094242</t>
+          <t>1118283</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2021073</t>
+          <t>2108345</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2021073</t>
+          <t>2108345</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2021073</t>
+          <t>2108345</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2920513</t>
+          <t>2927068</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2850514</t>
+          <t>2868717</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3036571</t>
+          <t>2978530</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3208677</t>
+          <t>3233269</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3160073</t>
+          <t>3191955</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3291561</t>
+          <t>3270933</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6129190</t>
+          <t>6160337</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6040436</t>
+          <t>6089655</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6261619</t>
+          <t>6221444</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>85,74%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>476728</t>
+          <t>537993</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368642</t>
+          <t>485319</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>540816</t>
+          <t>593230</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>398747</t>
+          <t>439962</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>319593</t>
+          <t>404162</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>442190</t>
+          <t>478418</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>875475</t>
+          <t>977955</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>760892</t>
+          <t>919849</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>956689</t>
+          <t>1046423</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>55289</t>
+          <t>60206</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39776</t>
+          <t>44235</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77503</t>
+          <t>80260</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>51696</t>
+          <t>57427</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38216</t>
+          <t>44932</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67394</t>
+          <t>75935</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>106985</t>
+          <t>117633</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84783</t>
+          <t>95811</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>132144</t>
+          <t>141205</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3452530</t>
+          <t>3525267</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3452530</t>
+          <t>3525267</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3452530</t>
+          <t>3525267</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3659120</t>
+          <t>3730658</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3659120</t>
+          <t>3730658</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3659120</t>
+          <t>3730658</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7111650</t>
+          <t>7255925</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7111650</t>
+          <t>7255925</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7111650</t>
+          <t>7255925</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
